--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.46957015447084</v>
+        <v>15.18880515010151</v>
       </c>
       <c r="D2" t="n">
-        <v>93.4663933229654</v>
+        <v>15.18828891498188</v>
       </c>
       <c r="E2" t="n">
-        <v>7.703630548168466</v>
+        <v>1.251839964077376</v>
       </c>
       <c r="F2" t="n">
-        <v>7.71656281826792</v>
+        <v>1.253941457968537</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.55444135311683</v>
+        <v>12.27759671988149</v>
       </c>
       <c r="D3" t="n">
-        <v>75.527142154099</v>
+        <v>12.27316060004109</v>
       </c>
       <c r="E3" t="n">
-        <v>7.703630548168466</v>
+        <v>1.251839964077376</v>
       </c>
       <c r="F3" t="n">
-        <v>7.71656281826792</v>
+        <v>1.253941457968537</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>79.37948431446145</v>
+        <v>12.89916620109999</v>
       </c>
       <c r="D4" t="n">
-        <v>79.34007418524816</v>
+        <v>12.89276205510283</v>
       </c>
       <c r="E4" t="n">
-        <v>7.703630548168466</v>
+        <v>1.251839964077376</v>
       </c>
       <c r="F4" t="n">
-        <v>7.71656281826792</v>
+        <v>1.253941457968537</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
